--- a/SAMPLE_CORRECT_FORMAT.xlsx
+++ b/SAMPLE_CORRECT_FORMAT.xlsx
@@ -4,121 +4,52 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Vietnam Electricity" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sample Data" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>2023-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>Date (YYYY-MM)</t>
+  </si>
+  <si>
+    <t>LocalCurrency/Unit</t>
+  </si>
+  <si>
+    <t>USD/Unit</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2024-01</t>
+  </si>
+  <si>
+    <t>January data</t>
+  </si>
+  <si>
+    <t>2024-02</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2023-02</t>
-  </si>
-  <si>
-    <t>2023-03</t>
-  </si>
-  <si>
-    <t>Tariff revision - EVN circular 1028</t>
-  </si>
-  <si>
-    <t>2023-04</t>
-  </si>
-  <si>
-    <t>2023-05</t>
-  </si>
-  <si>
-    <t>New base tariff effective May</t>
-  </si>
-  <si>
-    <t>2023-06</t>
-  </si>
-  <si>
-    <t>2023-07</t>
-  </si>
-  <si>
-    <t>2023-08</t>
-  </si>
-  <si>
-    <t>2023-09</t>
-  </si>
-  <si>
-    <t>2023-10</t>
-  </si>
-  <si>
-    <t>2023-11</t>
-  </si>
-  <si>
-    <t>2023-12</t>
-  </si>
-  <si>
-    <t>2024-01</t>
-  </si>
-  <si>
-    <t>Annual tariff adjustment</t>
-  </si>
-  <si>
-    <t>2024-02</t>
-  </si>
-  <si>
     <t>2024-03</t>
   </si>
   <si>
     <t>2024-04</t>
   </si>
   <si>
+    <t>Seasonal adjustment</t>
+  </si>
+  <si>
     <t>2024-05</t>
   </si>
   <si>
-    <t>Q2 adjustment</t>
-  </si>
-  <si>
-    <t>2024-06</t>
-  </si>
-  <si>
-    <t>2024-07</t>
-  </si>
-  <si>
-    <t>2024-08</t>
-  </si>
-  <si>
-    <t>2024-09</t>
-  </si>
-  <si>
-    <t>2024-10</t>
-  </si>
-  <si>
-    <t>2024-11</t>
-  </si>
-  <si>
-    <t>2024-12</t>
-  </si>
-  <si>
-    <t>2025-01</t>
-  </si>
-  <si>
-    <t>New tariff FY2025</t>
-  </si>
-  <si>
-    <t>2025-02</t>
-  </si>
-  <si>
-    <t>2025-03</t>
+    <t>© ARW Analytics Data Intelligence Platform. Licensed use only.</t>
   </si>
 </sst>
 </file>
@@ -135,6 +66,7 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -146,7 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F7"/>
+        <fgColor rgb="FF1A365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,7 +96,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,14 +438,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,302 +457,83 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>1650</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8500</v>
+      </c>
+      <c r="C2">
+        <v>30.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>1650</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8750</v>
+      </c>
+      <c r="C3">
+        <v>31.2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>1755</v>
-      </c>
-      <c r="C4" t="s">
+        <v>9100</v>
+      </c>
+      <c r="C4">
+        <v>32.8</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>1755</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8900</v>
+      </c>
+      <c r="C5">
+        <v>31.9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>1920</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>1920</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9300</v>
+      </c>
+      <c r="C6">
+        <v>33.4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
-      </c>
-      <c r="B8">
-        <v>1920</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>1920</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>1920</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>1920</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>1920</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>1920</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>1984</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>1984</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>1984</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17">
-        <v>1984</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18">
-        <v>2006</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>2006</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20">
-        <v>2006</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21">
-        <v>2006</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22">
-        <v>2006</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23">
-        <v>2006</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24">
-        <v>2006</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25">
-        <v>2006</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26">
-        <v>2103</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27">
-        <v>2103</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28">
-        <v>2103</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
